--- a/metrics/mobile-untracked-2026-03-20.xlsx
+++ b/metrics/mobile-untracked-2026-03-20.xlsx
@@ -60,7 +60,7 @@
     <t>medium</t>
   </si>
   <si>
-    <t>react-native, expo-image</t>
+    <t>expo-image, react-native</t>
   </si>
   <si>
     <t>Animated</t>
@@ -132,7 +132,7 @@
     <t>SkeletonText</t>
   </si>
   <si>
-    <t>../Ramp/Aggregator/components/SkeletonText, ../../../Ramp/Aggregator/components/SkeletonText, ./SkeletonText, ../SkeletonText, ../../components/SkeletonText</t>
+    <t>../Ramp/Aggregator/components/SkeletonText, ../../../Ramp/Aggregator/components/SkeletonText, ./SkeletonText, ../../components/SkeletonText, ../SkeletonText</t>
   </si>
   <si>
     <t>RewardsErrorBanner</t>
@@ -372,7 +372,7 @@
     <t>ListItemColumnEnd</t>
   </si>
   <si>
-    <t>./ListItemColumnEnd, ../ListItemColumnEnd, ../../components/ListItemColumnEnd</t>
+    <t>./ListItemColumnEnd, ../../components/ListItemColumnEnd, ../ListItemColumnEnd</t>
   </si>
   <si>
     <t>InfoRowSkeleton</t>
@@ -489,15 +489,15 @@
     <t>../../UI/SelectOptionSheet, ../../../../SelectOptionSheet</t>
   </si>
   <si>
+    <t>SectionList</t>
+  </si>
+  <si>
     <t>MaterialCommunityIcon</t>
   </si>
   <si>
     <t>react-native-vector-icons/MaterialCommunityIcons</t>
   </si>
   <si>
-    <t>SectionList</t>
-  </si>
-  <si>
     <t>EvilIcons</t>
   </si>
   <si>
@@ -570,6 +570,12 @@
     <t>FailedText</t>
   </si>
   <si>
+    <t>SnapUIAvatar</t>
+  </si>
+  <si>
+    <t>../SnapUIAvatar/SnapUIAvatar</t>
+  </si>
+  <si>
     <t>Children</t>
   </si>
   <si>
@@ -663,12 +669,6 @@
     <t>@react-native-community/checkbox</t>
   </si>
   <si>
-    <t>SnapUIAvatar</t>
-  </si>
-  <si>
-    <t>../SnapUIAvatar/SnapUIAvatar</t>
-  </si>
-  <si>
     <t>CaipAccountSelectorList</t>
   </si>
   <si>
@@ -678,7 +678,7 @@
     <t>EditSpendingCapButton</t>
   </si>
   <si>
-    <t>../../../Views/confirmations/components/edit-spending-cap-button, ../../edit-spending-cap-button/edit-spending-cap-button, ../../edit-spending-cap-button</t>
+    <t>../../../Views/confirmations/components/edit-spending-cap-button, ../../edit-spending-cap-button, ../../edit-spending-cap-button/edit-spending-cap-button</t>
   </si>
   <si>
     <t>TextWithTooltip</t>
@@ -810,6 +810,15 @@
     <t>CloseButton</t>
   </si>
   <si>
+    <t>SvgXml</t>
+  </si>
+  <si>
+    <t>AccountNetworkIndicator</t>
+  </si>
+  <si>
+    <t>../../UI/AccountNetworkIndicator, ../AccountNetworkIndicator/AccountNetworkIndicator</t>
+  </si>
+  <si>
     <t>GoogleIcon</t>
   </si>
   <si>
@@ -834,6 +843,12 @@
     <t>../../UI/DeFiPositions/DeFiPositionsList</t>
   </si>
   <si>
+    <t>SiteRowItemWrapper</t>
+  </si>
+  <si>
+    <t>../../UI/Sites/components/SiteRowItemWrapper/SiteRowItemWrapper, ../SiteRowItemWrapper/SiteRowItemWrapper</t>
+  </si>
+  <si>
     <t>TransactionsFooter</t>
   </si>
   <si>
@@ -852,12 +867,6 @@
     <t>../../UI/MultichainTransactionListItem</t>
   </si>
   <si>
-    <t>SiteRowItemWrapper</t>
-  </si>
-  <si>
-    <t>../../UI/Sites/components/SiteRowItemWrapper/SiteRowItemWrapper, ../SiteRowItemWrapper/SiteRowItemWrapper</t>
-  </si>
-  <si>
     <t>SRPList</t>
   </si>
   <si>
@@ -927,6 +936,12 @@
     <t>./AccountConnectMaliciousWarning/AccountConnectMaliciousWarning, ../../AccountConnect/AccountConnectMaliciousWarning/AccountConnectMaliciousWarning</t>
   </si>
   <si>
+    <t>WarningAlert</t>
+  </si>
+  <si>
+    <t>../../../components/UI/WarningAlert</t>
+  </si>
+  <si>
     <t>TrendingTokenLogo</t>
   </si>
   <si>
@@ -939,6 +954,12 @@
     <t>../Bridge/components/TransactionDetails/BridgeActivityItemTxSegments</t>
   </si>
   <si>
+    <t>AssetIcon</t>
+  </si>
+  <si>
+    <t>../AssetIcon</t>
+  </si>
+  <si>
     <t>TokenListSkeleton</t>
   </si>
   <si>
@@ -957,12 +978,6 @@
     <t>./TokenList/RemoveTokenBottomSheet, ../../../../UI/Tokens/TokenList/RemoveTokenBottomSheet</t>
   </si>
   <si>
-    <t>AssetIcon</t>
-  </si>
-  <si>
-    <t>../AssetIcon</t>
-  </si>
-  <si>
     <t>SrpInput</t>
   </si>
   <si>
@@ -1023,18 +1038,18 @@
     <t>UpdateRpcButton</t>
   </si>
   <si>
+    <t>TrustIcon</t>
+  </si>
+  <si>
+    <t>NameLabel</t>
+  </si>
+  <si>
     <t>AccountRightButton</t>
   </si>
   <si>
     <t>../AccountRightButton</t>
   </si>
   <si>
-    <t>TrustIcon</t>
-  </si>
-  <si>
-    <t>NameLabel</t>
-  </si>
-  <si>
     <t>DeFiProtocolPositionGroupTokens</t>
   </si>
   <si>
@@ -1053,12 +1068,6 @@
     <t>../../Base/RemoteImage/RemoteImageBadgeWrapper, ./RemoteImageBadgeWrapper</t>
   </si>
   <si>
-    <t>AccountNetworkIndicator</t>
-  </si>
-  <si>
-    <t>../AccountNetworkIndicator/AccountNetworkIndicator, ../../UI/AccountNetworkIndicator</t>
-  </si>
-  <si>
     <t>AnimatedCircle</t>
   </si>
   <si>
@@ -1074,15 +1083,6 @@
     <t>../../Views/confirmations/legacy/components/ApproveTransactionHeader, ../ApproveTransactionHeader</t>
   </si>
   <si>
-    <t>SvgXml</t>
-  </si>
-  <si>
-    <t>WarningAlert</t>
-  </si>
-  <si>
-    <t>../../../components/UI/WarningAlert</t>
-  </si>
-  <si>
     <t>EmptyIcon</t>
   </si>
   <si>
@@ -1116,24 +1116,24 @@
     <t>../../../UI/NetworkSelectorList/NetworkSelectorList, ../../../../components/UI/NetworkSelectorList/NetworkSelectorList</t>
   </si>
   <si>
+    <t>TokenDetailsStickyFooter</t>
+  </si>
+  <si>
+    <t>../components/TokenDetailsStickyFooter, ../../TokenDetails/components/TokenDetailsStickyFooter</t>
+  </si>
+  <si>
+    <t>TokenDetails</t>
+  </si>
+  <si>
+    <t>../../AssetOverview/TokenDetails</t>
+  </si>
+  <si>
     <t>MarketInsightsEntryCard</t>
   </si>
   <si>
     <t>../../MarketInsights, ../../../MarketInsights</t>
   </si>
   <si>
-    <t>TokenDetails</t>
-  </si>
-  <si>
-    <t>../../AssetOverview/TokenDetails</t>
-  </si>
-  <si>
-    <t>TokenDetailsStickyFooter</t>
-  </si>
-  <si>
-    <t>../components/TokenDetailsStickyFooter, ../../TokenDetails/components/TokenDetailsStickyFooter</t>
-  </si>
-  <si>
     <t>InlineAlert</t>
   </si>
   <si>
@@ -1170,15 +1170,15 @@
     <t>../status-icon, ../../status-icon</t>
   </si>
   <si>
+    <t>NetworkFilterTab</t>
+  </si>
+  <si>
     <t>PayTokenAmountSkeleton</t>
   </si>
   <si>
     <t>../../pay-token-amount</t>
   </si>
   <si>
-    <t>NetworkFilterTab</t>
-  </si>
-  <si>
     <t>AvatarTokenWithNetworkBadge</t>
   </si>
   <si>
@@ -1440,6 +1440,12 @@
     <t>../../../Stake/components/StakingConfirmation/AccountTag/AccountTag, ../AccountTag/AccountTag</t>
   </si>
   <si>
+    <t>CardScreenshotDeterrent</t>
+  </si>
+  <si>
+    <t>../CardScreenshotDeterrent/CardScreenshotDeterrent, ../../components/CardScreenshotDeterrent</t>
+  </si>
+  <si>
     <t>AssetCard</t>
   </si>
   <si>
@@ -1452,10 +1458,10 @@
     <t>../../components/CardImage/CardImage, ../../components/CardImage</t>
   </si>
   <si>
-    <t>CardScreenshotDeterrent</t>
-  </si>
-  <si>
-    <t>../../components/CardScreenshotDeterrent, ../CardScreenshotDeterrent/CardScreenshotDeterrent</t>
+    <t>TokenInputArea</t>
+  </si>
+  <si>
+    <t>../../components/TokenInputArea</t>
   </si>
   <si>
     <t>SkeletonItem</t>
@@ -1464,12 +1470,6 @@
     <t>../SkeletonItem</t>
   </si>
   <si>
-    <t>TokenInputArea</t>
-  </si>
-  <si>
-    <t>../../components/TokenInputArea</t>
-  </si>
-  <si>
     <t>CustomAmountSkeleton</t>
   </si>
   <si>
@@ -1488,18 +1488,42 @@
     <t>../../rows/pay-with-row</t>
   </si>
   <si>
+    <t>HeroRowSkeleton</t>
+  </si>
+  <si>
+    <t>../../rows/transactions/hero-row</t>
+  </si>
+  <si>
+    <t>SwitchAccountTypeInfoRow</t>
+  </si>
+  <si>
+    <t>../../rows/switch-account-type-info-row</t>
+  </si>
+  <si>
+    <t>Network</t>
+  </si>
+  <si>
+    <t>../../UI/info-row/info-value/network, ../../../UI/info-row/info-value/network</t>
+  </si>
+  <si>
+    <t>NetworkRow</t>
+  </si>
+  <si>
+    <t>../../rows/transactions/network-row, ../network-row</t>
+  </si>
+  <si>
+    <t>AlertModal</t>
+  </si>
+  <si>
+    <t>../alert-modal</t>
+  </si>
+  <si>
     <t>AccountNetworkRow</t>
   </si>
   <si>
     <t>./account-network-row, ../../../../confirmations/components/modals/switch-account-type-modal/account-network-row</t>
   </si>
   <si>
-    <t>AlertModal</t>
-  </si>
-  <si>
-    <t>../alert-modal</t>
-  </si>
-  <si>
     <t>GasModalHeader</t>
   </si>
   <si>
@@ -1512,30 +1536,6 @@
     <t>../../../components/gas/gas-input</t>
   </si>
   <si>
-    <t>HeroRowSkeleton</t>
-  </si>
-  <si>
-    <t>../../rows/transactions/hero-row</t>
-  </si>
-  <si>
-    <t>SwitchAccountTypeInfoRow</t>
-  </si>
-  <si>
-    <t>../../rows/switch-account-type-info-row</t>
-  </si>
-  <si>
-    <t>Network</t>
-  </si>
-  <si>
-    <t>../../UI/info-row/info-value/network, ../../../UI/info-row/info-value/network</t>
-  </si>
-  <si>
-    <t>NetworkRow</t>
-  </si>
-  <si>
-    <t>../../rows/transactions/network-row, ../network-row</t>
-  </si>
-  <si>
     <t>GasFeeTokenIcon</t>
   </si>
   <si>
@@ -1557,6 +1557,12 @@
     <t>HeaderBackButton</t>
   </si>
   <si>
+    <t>InfoAlert</t>
+  </si>
+  <si>
+    <t>../../components/InfoAlert</t>
+  </si>
+  <si>
     <t>NetworksFilterBar</t>
   </si>
   <si>
@@ -1566,12 +1572,6 @@
     <t>../../../Deposit/components/NetworksFilterBar, ../../../components/NetworksFilterBar</t>
   </si>
   <si>
-    <t>InfoAlert</t>
-  </si>
-  <si>
-    <t>../../components/InfoAlert</t>
-  </si>
-  <si>
     <t>View</t>
   </si>
   <si>
@@ -1716,18 +1716,18 @@
     <t>Circle</t>
   </si>
   <si>
+    <t>ApprovalModal</t>
+  </si>
+  <si>
+    <t>../../Approvals/ApprovalModal, ../ApprovalModal</t>
+  </si>
+  <si>
     <t>WebView</t>
   </si>
   <si>
     <t>@metamask/react-native-webview</t>
   </si>
   <si>
-    <t>ApprovalModal</t>
-  </si>
-  <si>
-    <t>../../Approvals/ApprovalModal, ../ApprovalModal</t>
-  </si>
-  <si>
     <t>Defs</t>
   </si>
   <si>
@@ -1773,7 +1773,7 @@
     <t>OnboardingStep</t>
   </si>
   <si>
-    <t>../../components/Onboarding/OnboardingStep, ./OnboardingStep</t>
+    <t>./OnboardingStep, ../../components/Onboarding/OnboardingStep</t>
   </si>
   <si>
     <t>GasFeesDetailsRow</t>
@@ -1863,6 +1863,12 @@
     <t>../../Deposit/components/PrivacySection, ../../components/PrivacySection</t>
   </si>
   <si>
+    <t>Tooltip</t>
+  </si>
+  <si>
+    <t>../../Views/confirmations/components/UI/Tooltip, ../UI/Tooltip, ../Tooltip/Tooltip</t>
+  </si>
+  <si>
     <t>ElevatedView</t>
   </si>
   <si>
@@ -1896,12 +1902,6 @@
     <t>../../Views/confirmations/components/UI/Tooltip/Tooltip, ../../Views/confirmations/components/UI/Tooltip, ../UI/Tooltip/Tooltip, ../Tooltip/Tooltip</t>
   </si>
   <si>
-    <t>Tooltip</t>
-  </si>
-  <si>
-    <t>../../Views/confirmations/components/UI/Tooltip, ../UI/Tooltip, ../Tooltip/Tooltip</t>
-  </si>
-  <si>
     <t>SelectComponent</t>
   </si>
   <si>
@@ -1947,6 +1947,18 @@
     <t>GenericEventDetails</t>
   </si>
   <si>
+    <t>TemplateRenderer</t>
+  </si>
+  <si>
+    <t>../../UI/TemplateRenderer, ../../../../../../UI/TemplateRenderer</t>
+  </si>
+  <si>
+    <t>DateTimePicker</t>
+  </si>
+  <si>
+    <t>@react-native-community/datetimepicker</t>
+  </si>
+  <si>
     <t>LottieView</t>
   </si>
   <si>
@@ -1965,39 +1977,27 @@
     <t>../../Base/InfoModal, ../../../Base/InfoModal</t>
   </si>
   <si>
+    <t>UnmountOnBlur</t>
+  </si>
+  <si>
+    <t>../../Views/UnmountOnBlur</t>
+  </si>
+  <si>
     <t>FadeIn</t>
   </si>
   <si>
     <t>react-native-fade-in-image</t>
   </si>
   <si>
-    <t>TemplateRenderer</t>
-  </si>
-  <si>
-    <t>../../UI/TemplateRenderer, ../../../../../../UI/TemplateRenderer</t>
-  </si>
-  <si>
     <t>SimulationDetailsLayout</t>
   </si>
   <si>
-    <t>UnmountOnBlur</t>
-  </si>
-  <si>
-    <t>../../Views/UnmountOnBlur</t>
-  </si>
-  <si>
     <t>Description</t>
   </si>
   <si>
     <t>./InfoDescription</t>
   </si>
   <si>
-    <t>DateTimePicker</t>
-  </si>
-  <si>
-    <t>@react-native-community/datetimepicker</t>
-  </si>
-  <si>
     <t>SwitchLoadingModal</t>
   </si>
   <si>
@@ -2277,6 +2277,12 @@
     <t>@tommasini/react-native-scrollable-tab-view/DefaultTabBar</t>
   </si>
   <si>
+    <t>SnapUIRenderer</t>
+  </si>
+  <si>
+    <t>./SnapUIRenderer, ../SnapUIRenderer/SnapUIRenderer</t>
+  </si>
+  <si>
     <t>SelectSRP</t>
   </si>
   <si>
@@ -2307,6 +2313,18 @@
     <t>../../UI/AddressCopy, ../../../../../UI/AddressCopy</t>
   </si>
   <si>
+    <t>ExploreSearchBar</t>
+  </si>
+  <si>
+    <t>./components/ExploreSearchBar/ExploreSearchBar, ../../components/ExploreSearchBar/ExploreSearchBar</t>
+  </si>
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>./components/Sections/Section, ../../../../Views/TrendingView/components/Sections/Section</t>
+  </si>
+  <si>
     <t>MultichainTransactionsFooter</t>
   </si>
   <si>
@@ -2325,18 +2343,6 @@
     <t>../../UI/Transactions/RetryModal, ./RetryModal</t>
   </si>
   <si>
-    <t>ExploreSearchBar</t>
-  </si>
-  <si>
-    <t>./components/ExploreSearchBar/ExploreSearchBar, ../../components/ExploreSearchBar/ExploreSearchBar</t>
-  </si>
-  <si>
-    <t>Section</t>
-  </si>
-  <si>
-    <t>./components/Sections/Section, ../../../../Views/TrendingView/components/Sections/Section</t>
-  </si>
-  <si>
     <t>Transactions</t>
   </si>
   <si>
@@ -2436,6 +2442,18 @@
     <t>../../UI/CollectibleOverview</t>
   </si>
   <si>
+    <t>RampRoutes</t>
+  </si>
+  <si>
+    <t>../../UI/Ramp/Aggregator/routes</t>
+  </si>
+  <si>
+    <t>SocialLoginIosUser</t>
+  </si>
+  <si>
+    <t>../../Views/SocialLoginIosUser</t>
+  </si>
+  <si>
     <t>Result</t>
   </si>
   <si>
@@ -2487,24 +2505,6 @@
     <t>AddressName</t>
   </si>
   <si>
-    <t>SnapUIRenderer</t>
-  </si>
-  <si>
-    <t>./SnapUIRenderer, ../SnapUIRenderer/SnapUIRenderer</t>
-  </si>
-  <si>
-    <t>RampRoutes</t>
-  </si>
-  <si>
-    <t>../../UI/Ramp/Aggregator/routes</t>
-  </si>
-  <si>
-    <t>SocialLoginIosUser</t>
-  </si>
-  <si>
-    <t>../../Views/SocialLoginIosUser</t>
-  </si>
-  <si>
     <t>Option</t>
   </si>
   <si>
@@ -2880,6 +2880,33 @@
     <t>../../UI/info-row/info-value/display-url, ../../../UI/info-row/info-value/display-url</t>
   </si>
   <si>
+    <t>PredictClaimBackground</t>
+  </si>
+  <si>
+    <t>../../predict-confirmations/predict-claim-background</t>
+  </si>
+  <si>
+    <t>BridgeFeeRow</t>
+  </si>
+  <si>
+    <t>../../rows/bridge-fee-row</t>
+  </si>
+  <si>
+    <t>TotalRow</t>
+  </si>
+  <si>
+    <t>../../rows/total-row</t>
+  </si>
+  <si>
+    <t>PercentageRow</t>
+  </si>
+  <si>
+    <t>../../rows/percentage-row</t>
+  </si>
+  <si>
+    <t>PayWithRow</t>
+  </si>
+  <si>
     <t>GasSpeed</t>
   </si>
   <si>
@@ -2892,33 +2919,6 @@
     <t>../gas-fee-modal, ../../../modals/gas-fee-modal</t>
   </si>
   <si>
-    <t>PredictClaimBackground</t>
-  </si>
-  <si>
-    <t>../../predict-confirmations/predict-claim-background</t>
-  </si>
-  <si>
-    <t>BridgeFeeRow</t>
-  </si>
-  <si>
-    <t>../../rows/bridge-fee-row</t>
-  </si>
-  <si>
-    <t>TotalRow</t>
-  </si>
-  <si>
-    <t>../../rows/total-row</t>
-  </si>
-  <si>
-    <t>PercentageRow</t>
-  </si>
-  <si>
-    <t>../../rows/percentage-row</t>
-  </si>
-  <si>
-    <t>PayWithRow</t>
-  </si>
-  <si>
     <t>NFTInfoRow</t>
   </si>
   <si>
@@ -2964,16 +2964,16 @@
     <t>../../../UI/info-row/info-value/address</t>
   </si>
   <si>
+    <t>PredictMarketOutcomeResolved</t>
+  </si>
+  <si>
+    <t>../../../../components/PredictMarketOutcomeResolved</t>
+  </si>
+  <si>
     <t>PredictPositionDetail</t>
   </si>
   <si>
     <t>../../../../components/PredictPositionDetail</t>
-  </si>
-  <si>
-    <t>PredictMarketOutcomeResolved</t>
-  </si>
-  <si>
-    <t>../../../../components/PredictMarketOutcomeResolved</t>
   </si>
   <si>
     <t>PermitSimulationValueDisplay</t>
@@ -5063,16 +5063,16 @@
         <v>4</v>
       </c>
       <c r="D72">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E72" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F72" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G72" t="s">
-        <v>159</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
@@ -5080,22 +5080,22 @@
         <v>72</v>
       </c>
       <c r="B73" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C73">
         <v>4</v>
       </c>
       <c r="D73">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E73" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F73" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G73" t="s">
-        <v>28</v>
+        <v>160</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
@@ -5408,16 +5408,16 @@
         <v>3</v>
       </c>
       <c r="D87">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E87" t="s">
+        <v>103</v>
+      </c>
+      <c r="F87" t="s">
+        <v>14</v>
+      </c>
+      <c r="G87" t="s">
         <v>186</v>
-      </c>
-      <c r="F87" t="s">
-        <v>14</v>
-      </c>
-      <c r="G87" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
@@ -5431,16 +5431,16 @@
         <v>3</v>
       </c>
       <c r="D88">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E88" t="s">
-        <v>32</v>
+        <v>188</v>
       </c>
       <c r="F88" t="s">
         <v>14</v>
       </c>
       <c r="G88" t="s">
-        <v>188</v>
+        <v>86</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.25">
@@ -5454,16 +5454,16 @@
         <v>3</v>
       </c>
       <c r="D89">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E89" t="s">
+        <v>32</v>
+      </c>
+      <c r="F89" t="s">
+        <v>14</v>
+      </c>
+      <c r="G89" t="s">
         <v>190</v>
-      </c>
-      <c r="F89" t="s">
-        <v>14</v>
-      </c>
-      <c r="G89" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.25">
@@ -5471,22 +5471,22 @@
         <v>89</v>
       </c>
       <c r="B90" t="s">
+        <v>191</v>
+      </c>
+      <c r="C90">
+        <v>3</v>
+      </c>
+      <c r="D90">
+        <v>3</v>
+      </c>
+      <c r="E90" t="s">
         <v>192</v>
       </c>
-      <c r="C90">
-        <v>3</v>
-      </c>
-      <c r="D90">
-        <v>3</v>
-      </c>
-      <c r="E90" t="s">
+      <c r="F90" t="s">
+        <v>14</v>
+      </c>
+      <c r="G90" t="s">
         <v>193</v>
-      </c>
-      <c r="F90" t="s">
-        <v>14</v>
-      </c>
-      <c r="G90" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.25">
@@ -5494,22 +5494,22 @@
         <v>90</v>
       </c>
       <c r="B91" t="s">
+        <v>194</v>
+      </c>
+      <c r="C91">
+        <v>3</v>
+      </c>
+      <c r="D91">
+        <v>3</v>
+      </c>
+      <c r="E91" t="s">
         <v>195</v>
       </c>
-      <c r="C91">
-        <v>3</v>
-      </c>
-      <c r="D91">
-        <v>3</v>
-      </c>
-      <c r="E91" t="s">
-        <v>36</v>
-      </c>
       <c r="F91" t="s">
         <v>14</v>
       </c>
       <c r="G91" t="s">
-        <v>159</v>
+        <v>196</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
@@ -5517,22 +5517,22 @@
         <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C92">
         <v>3</v>
       </c>
       <c r="D92">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E92" t="s">
         <v>36</v>
       </c>
       <c r="F92" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G92" t="s">
-        <v>197</v>
+        <v>160</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.25">
@@ -5546,13 +5546,13 @@
         <v>3</v>
       </c>
       <c r="D93">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E93" t="s">
-        <v>17</v>
+        <v>36</v>
       </c>
       <c r="F93" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G93" t="s">
         <v>199</v>
@@ -5572,7 +5572,7 @@
         <v>3</v>
       </c>
       <c r="E94" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="F94" t="s">
         <v>14</v>
@@ -5595,7 +5595,7 @@
         <v>3</v>
       </c>
       <c r="E95" t="s">
-        <v>103</v>
+        <v>51</v>
       </c>
       <c r="F95" t="s">
         <v>14</v>
@@ -5618,7 +5618,7 @@
         <v>3</v>
       </c>
       <c r="E96" t="s">
-        <v>193</v>
+        <v>103</v>
       </c>
       <c r="F96" t="s">
         <v>14</v>
@@ -5641,7 +5641,7 @@
         <v>3</v>
       </c>
       <c r="E97" t="s">
-        <v>103</v>
+        <v>195</v>
       </c>
       <c r="F97" t="s">
         <v>14</v>
@@ -5661,13 +5661,13 @@
         <v>3</v>
       </c>
       <c r="D98">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E98" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="F98" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G98" t="s">
         <v>209</v>
@@ -5687,13 +5687,13 @@
         <v>1</v>
       </c>
       <c r="E99" t="s">
+        <v>24</v>
+      </c>
+      <c r="F99" t="s">
+        <v>21</v>
+      </c>
+      <c r="G99" t="s">
         <v>211</v>
-      </c>
-      <c r="F99" t="s">
-        <v>14</v>
-      </c>
-      <c r="G99" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.25">
@@ -5701,22 +5701,22 @@
         <v>99</v>
       </c>
       <c r="B100" t="s">
+        <v>212</v>
+      </c>
+      <c r="C100">
+        <v>3</v>
+      </c>
+      <c r="D100">
+        <v>1</v>
+      </c>
+      <c r="E100" t="s">
         <v>213</v>
       </c>
-      <c r="C100">
-        <v>3</v>
-      </c>
-      <c r="D100">
-        <v>3</v>
-      </c>
-      <c r="E100" t="s">
+      <c r="F100" t="s">
+        <v>14</v>
+      </c>
+      <c r="G100" t="s">
         <v>214</v>
-      </c>
-      <c r="F100" t="s">
-        <v>8</v>
-      </c>
-      <c r="G100" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.25">
@@ -5724,19 +5724,19 @@
         <v>100</v>
       </c>
       <c r="B101" t="s">
+        <v>215</v>
+      </c>
+      <c r="C101">
+        <v>3</v>
+      </c>
+      <c r="D101">
+        <v>3</v>
+      </c>
+      <c r="E101" t="s">
         <v>216</v>
       </c>
-      <c r="C101">
-        <v>3</v>
-      </c>
-      <c r="D101">
-        <v>2</v>
-      </c>
-      <c r="E101" t="s">
-        <v>103</v>
-      </c>
       <c r="F101" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="G101" t="s">
         <v>217</v>
@@ -6078,7 +6078,7 @@
         <v>2</v>
       </c>
       <c r="E116" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F116" t="s">
         <v>14</v>
@@ -6354,13 +6354,13 @@
         <v>2</v>
       </c>
       <c r="E128" t="s">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="F128" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G128" t="s">
-        <v>266</v>
+        <v>47</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.25">
@@ -6368,22 +6368,22 @@
         <v>128</v>
       </c>
       <c r="B129" t="s">
+        <v>266</v>
+      </c>
+      <c r="C129">
+        <v>2</v>
+      </c>
+      <c r="D129">
+        <v>2</v>
+      </c>
+      <c r="E129" t="s">
+        <v>103</v>
+      </c>
+      <c r="F129" t="s">
+        <v>14</v>
+      </c>
+      <c r="G129" t="s">
         <v>267</v>
-      </c>
-      <c r="C129">
-        <v>2</v>
-      </c>
-      <c r="D129">
-        <v>2</v>
-      </c>
-      <c r="E129" t="s">
-        <v>36</v>
-      </c>
-      <c r="F129" t="s">
-        <v>21</v>
-      </c>
-      <c r="G129" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.25">
@@ -6391,7 +6391,7 @@
         <v>129</v>
       </c>
       <c r="B130" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C130">
         <v>2</v>
@@ -6406,7 +6406,7 @@
         <v>21</v>
       </c>
       <c r="G130" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.25">
@@ -6414,22 +6414,22 @@
         <v>130</v>
       </c>
       <c r="B131" t="s">
+        <v>270</v>
+      </c>
+      <c r="C131">
+        <v>2</v>
+      </c>
+      <c r="D131">
+        <v>2</v>
+      </c>
+      <c r="E131" t="s">
+        <v>36</v>
+      </c>
+      <c r="F131" t="s">
+        <v>21</v>
+      </c>
+      <c r="G131" t="s">
         <v>271</v>
-      </c>
-      <c r="C131">
-        <v>2</v>
-      </c>
-      <c r="D131">
-        <v>2</v>
-      </c>
-      <c r="E131" t="s">
-        <v>32</v>
-      </c>
-      <c r="F131" t="s">
-        <v>14</v>
-      </c>
-      <c r="G131" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.25">
@@ -6437,22 +6437,22 @@
         <v>131</v>
       </c>
       <c r="B132" t="s">
+        <v>272</v>
+      </c>
+      <c r="C132">
+        <v>2</v>
+      </c>
+      <c r="D132">
+        <v>2</v>
+      </c>
+      <c r="E132" t="s">
+        <v>36</v>
+      </c>
+      <c r="F132" t="s">
+        <v>21</v>
+      </c>
+      <c r="G132" t="s">
         <v>273</v>
-      </c>
-      <c r="C132">
-        <v>2</v>
-      </c>
-      <c r="D132">
-        <v>2</v>
-      </c>
-      <c r="E132" t="s">
-        <v>173</v>
-      </c>
-      <c r="F132" t="s">
-        <v>14</v>
-      </c>
-      <c r="G132" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.25">
@@ -6460,22 +6460,22 @@
         <v>132</v>
       </c>
       <c r="B133" t="s">
+        <v>274</v>
+      </c>
+      <c r="C133">
+        <v>2</v>
+      </c>
+      <c r="D133">
+        <v>2</v>
+      </c>
+      <c r="E133" t="s">
+        <v>32</v>
+      </c>
+      <c r="F133" t="s">
+        <v>14</v>
+      </c>
+      <c r="G133" t="s">
         <v>275</v>
-      </c>
-      <c r="C133">
-        <v>2</v>
-      </c>
-      <c r="D133">
-        <v>2</v>
-      </c>
-      <c r="E133" t="s">
-        <v>30</v>
-      </c>
-      <c r="F133" t="s">
-        <v>21</v>
-      </c>
-      <c r="G133" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.25">
@@ -6483,22 +6483,22 @@
         <v>133</v>
       </c>
       <c r="B134" t="s">
+        <v>276</v>
+      </c>
+      <c r="C134">
+        <v>2</v>
+      </c>
+      <c r="D134">
+        <v>2</v>
+      </c>
+      <c r="E134" t="s">
+        <v>213</v>
+      </c>
+      <c r="F134" t="s">
+        <v>14</v>
+      </c>
+      <c r="G134" t="s">
         <v>277</v>
-      </c>
-      <c r="C134">
-        <v>2</v>
-      </c>
-      <c r="D134">
-        <v>2</v>
-      </c>
-      <c r="E134" t="s">
-        <v>30</v>
-      </c>
-      <c r="F134" t="s">
-        <v>21</v>
-      </c>
-      <c r="G134" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.25">
@@ -6506,22 +6506,22 @@
         <v>134</v>
       </c>
       <c r="B135" t="s">
+        <v>278</v>
+      </c>
+      <c r="C135">
+        <v>2</v>
+      </c>
+      <c r="D135">
+        <v>2</v>
+      </c>
+      <c r="E135" t="s">
+        <v>173</v>
+      </c>
+      <c r="F135" t="s">
+        <v>14</v>
+      </c>
+      <c r="G135" t="s">
         <v>279</v>
-      </c>
-      <c r="C135">
-        <v>2</v>
-      </c>
-      <c r="D135">
-        <v>2</v>
-      </c>
-      <c r="E135" t="s">
-        <v>211</v>
-      </c>
-      <c r="F135" t="s">
-        <v>14</v>
-      </c>
-      <c r="G135" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.25">
@@ -6529,7 +6529,7 @@
         <v>135</v>
       </c>
       <c r="B136" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C136">
         <v>2</v>
@@ -6541,10 +6541,10 @@
         <v>30</v>
       </c>
       <c r="F136" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G136" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.25">
@@ -6552,7 +6552,7 @@
         <v>136</v>
       </c>
       <c r="B137" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C137">
         <v>2</v>
@@ -6561,13 +6561,13 @@
         <v>2</v>
       </c>
       <c r="E137" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="F137" t="s">
         <v>21</v>
       </c>
       <c r="G137" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.25">
@@ -6575,22 +6575,22 @@
         <v>137</v>
       </c>
       <c r="B138" t="s">
+        <v>284</v>
+      </c>
+      <c r="C138">
+        <v>2</v>
+      </c>
+      <c r="D138">
+        <v>2</v>
+      </c>
+      <c r="E138" t="s">
+        <v>30</v>
+      </c>
+      <c r="F138" t="s">
+        <v>14</v>
+      </c>
+      <c r="G138" t="s">
         <v>285</v>
-      </c>
-      <c r="C138">
-        <v>2</v>
-      </c>
-      <c r="D138">
-        <v>2</v>
-      </c>
-      <c r="E138" t="s">
-        <v>286</v>
-      </c>
-      <c r="F138" t="s">
-        <v>14</v>
-      </c>
-      <c r="G138" t="s">
-        <v>287</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.25">
@@ -6598,7 +6598,7 @@
         <v>138</v>
       </c>
       <c r="B139" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C139">
         <v>2</v>
@@ -6607,13 +6607,13 @@
         <v>2</v>
       </c>
       <c r="E139" t="s">
-        <v>77</v>
+        <v>36</v>
       </c>
       <c r="F139" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G139" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.25">
@@ -6621,22 +6621,22 @@
         <v>139</v>
       </c>
       <c r="B140" t="s">
+        <v>288</v>
+      </c>
+      <c r="C140">
+        <v>2</v>
+      </c>
+      <c r="D140">
+        <v>2</v>
+      </c>
+      <c r="E140" t="s">
+        <v>289</v>
+      </c>
+      <c r="F140" t="s">
+        <v>14</v>
+      </c>
+      <c r="G140" t="s">
         <v>290</v>
-      </c>
-      <c r="C140">
-        <v>2</v>
-      </c>
-      <c r="D140">
-        <v>2</v>
-      </c>
-      <c r="E140" t="s">
-        <v>27</v>
-      </c>
-      <c r="F140" t="s">
-        <v>14</v>
-      </c>
-      <c r="G140" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.25">
@@ -6644,22 +6644,22 @@
         <v>140</v>
       </c>
       <c r="B141" t="s">
+        <v>291</v>
+      </c>
+      <c r="C141">
+        <v>2</v>
+      </c>
+      <c r="D141">
+        <v>2</v>
+      </c>
+      <c r="E141" t="s">
+        <v>77</v>
+      </c>
+      <c r="F141" t="s">
+        <v>14</v>
+      </c>
+      <c r="G141" t="s">
         <v>292</v>
-      </c>
-      <c r="C141">
-        <v>2</v>
-      </c>
-      <c r="D141">
-        <v>2</v>
-      </c>
-      <c r="E141" t="s">
-        <v>54</v>
-      </c>
-      <c r="F141" t="s">
-        <v>14</v>
-      </c>
-      <c r="G141" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.25">
@@ -6667,22 +6667,22 @@
         <v>141</v>
       </c>
       <c r="B142" t="s">
+        <v>293</v>
+      </c>
+      <c r="C142">
+        <v>2</v>
+      </c>
+      <c r="D142">
+        <v>2</v>
+      </c>
+      <c r="E142" t="s">
+        <v>27</v>
+      </c>
+      <c r="F142" t="s">
+        <v>14</v>
+      </c>
+      <c r="G142" t="s">
         <v>294</v>
-      </c>
-      <c r="C142">
-        <v>2</v>
-      </c>
-      <c r="D142">
-        <v>2</v>
-      </c>
-      <c r="E142" t="s">
-        <v>51</v>
-      </c>
-      <c r="F142" t="s">
-        <v>14</v>
-      </c>
-      <c r="G142" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.25">
@@ -6690,22 +6690,22 @@
         <v>142</v>
       </c>
       <c r="B143" t="s">
+        <v>295</v>
+      </c>
+      <c r="C143">
+        <v>2</v>
+      </c>
+      <c r="D143">
+        <v>2</v>
+      </c>
+      <c r="E143" t="s">
+        <v>54</v>
+      </c>
+      <c r="F143" t="s">
+        <v>14</v>
+      </c>
+      <c r="G143" t="s">
         <v>296</v>
-      </c>
-      <c r="C143">
-        <v>2</v>
-      </c>
-      <c r="D143">
-        <v>2</v>
-      </c>
-      <c r="E143" t="s">
-        <v>41</v>
-      </c>
-      <c r="F143" t="s">
-        <v>14</v>
-      </c>
-      <c r="G143" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.25">
@@ -6713,22 +6713,22 @@
         <v>143</v>
       </c>
       <c r="B144" t="s">
+        <v>297</v>
+      </c>
+      <c r="C144">
+        <v>2</v>
+      </c>
+      <c r="D144">
+        <v>2</v>
+      </c>
+      <c r="E144" t="s">
+        <v>51</v>
+      </c>
+      <c r="F144" t="s">
+        <v>14</v>
+      </c>
+      <c r="G144" t="s">
         <v>298</v>
-      </c>
-      <c r="C144">
-        <v>2</v>
-      </c>
-      <c r="D144">
-        <v>2</v>
-      </c>
-      <c r="E144" t="s">
-        <v>32</v>
-      </c>
-      <c r="F144" t="s">
-        <v>21</v>
-      </c>
-      <c r="G144" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.25">
@@ -6736,22 +6736,22 @@
         <v>144</v>
       </c>
       <c r="B145" t="s">
+        <v>299</v>
+      </c>
+      <c r="C145">
+        <v>2</v>
+      </c>
+      <c r="D145">
+        <v>2</v>
+      </c>
+      <c r="E145" t="s">
+        <v>41</v>
+      </c>
+      <c r="F145" t="s">
+        <v>14</v>
+      </c>
+      <c r="G145" t="s">
         <v>300</v>
-      </c>
-      <c r="C145">
-        <v>2</v>
-      </c>
-      <c r="D145">
-        <v>2</v>
-      </c>
-      <c r="E145" t="s">
-        <v>54</v>
-      </c>
-      <c r="F145" t="s">
-        <v>21</v>
-      </c>
-      <c r="G145" t="s">
-        <v>301</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.25">
@@ -6759,22 +6759,22 @@
         <v>145</v>
       </c>
       <c r="B146" t="s">
+        <v>301</v>
+      </c>
+      <c r="C146">
+        <v>2</v>
+      </c>
+      <c r="D146">
+        <v>2</v>
+      </c>
+      <c r="E146" t="s">
+        <v>32</v>
+      </c>
+      <c r="F146" t="s">
+        <v>21</v>
+      </c>
+      <c r="G146" t="s">
         <v>302</v>
-      </c>
-      <c r="C146">
-        <v>2</v>
-      </c>
-      <c r="D146">
-        <v>2</v>
-      </c>
-      <c r="E146" t="s">
-        <v>103</v>
-      </c>
-      <c r="F146" t="s">
-        <v>14</v>
-      </c>
-      <c r="G146" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.25">
@@ -6782,22 +6782,22 @@
         <v>146</v>
       </c>
       <c r="B147" t="s">
+        <v>303</v>
+      </c>
+      <c r="C147">
+        <v>2</v>
+      </c>
+      <c r="D147">
+        <v>2</v>
+      </c>
+      <c r="E147" t="s">
+        <v>54</v>
+      </c>
+      <c r="F147" t="s">
+        <v>21</v>
+      </c>
+      <c r="G147" t="s">
         <v>304</v>
-      </c>
-      <c r="C147">
-        <v>2</v>
-      </c>
-      <c r="D147">
-        <v>2</v>
-      </c>
-      <c r="E147" t="s">
-        <v>51</v>
-      </c>
-      <c r="F147" t="s">
-        <v>14</v>
-      </c>
-      <c r="G147" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.25">
@@ -6805,22 +6805,22 @@
         <v>147</v>
       </c>
       <c r="B148" t="s">
+        <v>305</v>
+      </c>
+      <c r="C148">
+        <v>2</v>
+      </c>
+      <c r="D148">
+        <v>2</v>
+      </c>
+      <c r="E148" t="s">
+        <v>103</v>
+      </c>
+      <c r="F148" t="s">
+        <v>14</v>
+      </c>
+      <c r="G148" t="s">
         <v>306</v>
-      </c>
-      <c r="C148">
-        <v>2</v>
-      </c>
-      <c r="D148">
-        <v>2</v>
-      </c>
-      <c r="E148" t="s">
-        <v>32</v>
-      </c>
-      <c r="F148" t="s">
-        <v>14</v>
-      </c>
-      <c r="G148" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.25">
@@ -6828,22 +6828,22 @@
         <v>148</v>
       </c>
       <c r="B149" t="s">
+        <v>307</v>
+      </c>
+      <c r="C149">
+        <v>2</v>
+      </c>
+      <c r="D149">
+        <v>1</v>
+      </c>
+      <c r="E149" t="s">
+        <v>41</v>
+      </c>
+      <c r="F149" t="s">
+        <v>14</v>
+      </c>
+      <c r="G149" t="s">
         <v>308</v>
-      </c>
-      <c r="C149">
-        <v>2</v>
-      </c>
-      <c r="D149">
-        <v>2</v>
-      </c>
-      <c r="E149" t="s">
-        <v>20</v>
-      </c>
-      <c r="F149" t="s">
-        <v>21</v>
-      </c>
-      <c r="G149" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.25">
@@ -6851,22 +6851,22 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
+        <v>309</v>
+      </c>
+      <c r="C150">
+        <v>2</v>
+      </c>
+      <c r="D150">
+        <v>2</v>
+      </c>
+      <c r="E150" t="s">
+        <v>51</v>
+      </c>
+      <c r="F150" t="s">
+        <v>14</v>
+      </c>
+      <c r="G150" t="s">
         <v>310</v>
-      </c>
-      <c r="C150">
-        <v>2</v>
-      </c>
-      <c r="D150">
-        <v>2</v>
-      </c>
-      <c r="E150" t="s">
-        <v>30</v>
-      </c>
-      <c r="F150" t="s">
-        <v>14</v>
-      </c>
-      <c r="G150" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.25">
@@ -6874,22 +6874,22 @@
         <v>150</v>
       </c>
       <c r="B151" t="s">
+        <v>311</v>
+      </c>
+      <c r="C151">
+        <v>2</v>
+      </c>
+      <c r="D151">
+        <v>2</v>
+      </c>
+      <c r="E151" t="s">
+        <v>32</v>
+      </c>
+      <c r="F151" t="s">
+        <v>14</v>
+      </c>
+      <c r="G151" t="s">
         <v>312</v>
-      </c>
-      <c r="C151">
-        <v>2</v>
-      </c>
-      <c r="D151">
-        <v>2</v>
-      </c>
-      <c r="E151" t="s">
-        <v>54</v>
-      </c>
-      <c r="F151" t="s">
-        <v>21</v>
-      </c>
-      <c r="G151" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.25">
@@ -6897,7 +6897,7 @@
         <v>151</v>
       </c>
       <c r="B152" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C152">
         <v>2</v>
@@ -6912,7 +6912,7 @@
         <v>21</v>
       </c>
       <c r="G152" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.25">
@@ -6920,22 +6920,22 @@
         <v>152</v>
       </c>
       <c r="B153" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C153">
         <v>2</v>
       </c>
       <c r="D153">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E153" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="F153" t="s">
         <v>21</v>
       </c>
       <c r="G153" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.25">
@@ -6943,22 +6943,22 @@
         <v>153</v>
       </c>
       <c r="B154" t="s">
+        <v>317</v>
+      </c>
+      <c r="C154">
+        <v>2</v>
+      </c>
+      <c r="D154">
+        <v>2</v>
+      </c>
+      <c r="E154" t="s">
+        <v>30</v>
+      </c>
+      <c r="F154" t="s">
+        <v>14</v>
+      </c>
+      <c r="G154" t="s">
         <v>318</v>
-      </c>
-      <c r="C154">
-        <v>2</v>
-      </c>
-      <c r="D154">
-        <v>1</v>
-      </c>
-      <c r="E154" t="s">
-        <v>32</v>
-      </c>
-      <c r="F154" t="s">
-        <v>14</v>
-      </c>
-      <c r="G154" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.25">
@@ -6966,7 +6966,7 @@
         <v>154</v>
       </c>
       <c r="B155" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C155">
         <v>2</v>
@@ -6975,13 +6975,13 @@
         <v>2</v>
       </c>
       <c r="E155" t="s">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="F155" t="s">
         <v>21</v>
       </c>
       <c r="G155" t="s">
-        <v>123</v>
+        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.25">
@@ -6995,10 +6995,10 @@
         <v>2</v>
       </c>
       <c r="D156">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E156" t="s">
-        <v>116</v>
+        <v>27</v>
       </c>
       <c r="F156" t="s">
         <v>21</v>
@@ -7018,10 +7018,10 @@
         <v>2</v>
       </c>
       <c r="D157">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E157" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="F157" t="s">
         <v>14</v>
@@ -7050,7 +7050,7 @@
         <v>21</v>
       </c>
       <c r="G158" t="s">
-        <v>326</v>
+        <v>123</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.25">
@@ -7058,22 +7058,22 @@
         <v>158</v>
       </c>
       <c r="B159" t="s">
+        <v>326</v>
+      </c>
+      <c r="C159">
+        <v>2</v>
+      </c>
+      <c r="D159">
+        <v>2</v>
+      </c>
+      <c r="E159" t="s">
+        <v>116</v>
+      </c>
+      <c r="F159" t="s">
+        <v>21</v>
+      </c>
+      <c r="G159" t="s">
         <v>327</v>
-      </c>
-      <c r="C159">
-        <v>2</v>
-      </c>
-      <c r="D159">
-        <v>2</v>
-      </c>
-      <c r="E159" t="s">
-        <v>32</v>
-      </c>
-      <c r="F159" t="s">
-        <v>14</v>
-      </c>
-      <c r="G159" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.25">
@@ -7081,22 +7081,22 @@
         <v>159</v>
       </c>
       <c r="B160" t="s">
+        <v>328</v>
+      </c>
+      <c r="C160">
+        <v>2</v>
+      </c>
+      <c r="D160">
+        <v>2</v>
+      </c>
+      <c r="E160" t="s">
+        <v>17</v>
+      </c>
+      <c r="F160" t="s">
+        <v>14</v>
+      </c>
+      <c r="G160" t="s">
         <v>329</v>
-      </c>
-      <c r="C160">
-        <v>2</v>
-      </c>
-      <c r="D160">
-        <v>2</v>
-      </c>
-      <c r="E160" t="s">
-        <v>103</v>
-      </c>
-      <c r="F160" t="s">
-        <v>14</v>
-      </c>
-      <c r="G160" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.25">
@@ -7104,22 +7104,22 @@
         <v>160</v>
       </c>
       <c r="B161" t="s">
+        <v>330</v>
+      </c>
+      <c r="C161">
+        <v>2</v>
+      </c>
+      <c r="D161">
+        <v>2</v>
+      </c>
+      <c r="E161" t="s">
+        <v>36</v>
+      </c>
+      <c r="F161" t="s">
+        <v>21</v>
+      </c>
+      <c r="G161" t="s">
         <v>331</v>
-      </c>
-      <c r="C161">
-        <v>2</v>
-      </c>
-      <c r="D161">
-        <v>2</v>
-      </c>
-      <c r="E161" t="s">
-        <v>77</v>
-      </c>
-      <c r="F161" t="s">
-        <v>14</v>
-      </c>
-      <c r="G161" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.25">
@@ -7127,22 +7127,22 @@
         <v>161</v>
       </c>
       <c r="B162" t="s">
+        <v>332</v>
+      </c>
+      <c r="C162">
+        <v>2</v>
+      </c>
+      <c r="D162">
+        <v>2</v>
+      </c>
+      <c r="E162" t="s">
+        <v>32</v>
+      </c>
+      <c r="F162" t="s">
+        <v>14</v>
+      </c>
+      <c r="G162" t="s">
         <v>333</v>
-      </c>
-      <c r="C162">
-        <v>2</v>
-      </c>
-      <c r="D162">
-        <v>1</v>
-      </c>
-      <c r="E162" t="s">
-        <v>24</v>
-      </c>
-      <c r="F162" t="s">
-        <v>21</v>
-      </c>
-      <c r="G162" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.25">
@@ -7156,16 +7156,16 @@
         <v>2</v>
       </c>
       <c r="D163">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E163" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="F163" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G163" t="s">
-        <v>86</v>
+        <v>335</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.25">
@@ -7173,22 +7173,22 @@
         <v>163</v>
       </c>
       <c r="B164" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C164">
         <v>2</v>
       </c>
       <c r="D164">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E164" t="s">
-        <v>24</v>
+        <v>77</v>
       </c>
       <c r="F164" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G164" t="s">
-        <v>86</v>
+        <v>337</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.25">
@@ -7196,13 +7196,13 @@
         <v>164</v>
       </c>
       <c r="B165" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C165">
         <v>2</v>
       </c>
       <c r="D165">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E165" t="s">
         <v>24</v>
@@ -7211,7 +7211,7 @@
         <v>21</v>
       </c>
       <c r="G165" t="s">
-        <v>337</v>
+        <v>86</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.25">
@@ -7219,7 +7219,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="C166">
         <v>2</v>
@@ -7228,7 +7228,7 @@
         <v>1</v>
       </c>
       <c r="E166" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="F166" t="s">
         <v>21</v>
@@ -7242,7 +7242,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="C167">
         <v>2</v>
@@ -7251,7 +7251,7 @@
         <v>1</v>
       </c>
       <c r="E167" t="s">
-        <v>141</v>
+        <v>24</v>
       </c>
       <c r="F167" t="s">
         <v>21</v>
@@ -7265,7 +7265,7 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C168">
         <v>2</v>
@@ -7274,13 +7274,13 @@
         <v>1</v>
       </c>
       <c r="E168" t="s">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="F168" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G168" t="s">
-        <v>341</v>
+        <v>86</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.25">
@@ -7294,16 +7294,16 @@
         <v>2</v>
       </c>
       <c r="D169">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E169" t="s">
-        <v>32</v>
+        <v>141</v>
       </c>
       <c r="F169" t="s">
         <v>21</v>
       </c>
       <c r="G169" t="s">
-        <v>343</v>
+        <v>86</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.25">
@@ -7311,7 +7311,7 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="C170">
         <v>2</v>
@@ -7320,13 +7320,13 @@
         <v>2</v>
       </c>
       <c r="E170" t="s">
-        <v>211</v>
+        <v>24</v>
       </c>
       <c r="F170" t="s">
         <v>21</v>
       </c>
       <c r="G170" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.25">
@@ -7334,22 +7334,22 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
+        <v>345</v>
+      </c>
+      <c r="C171">
+        <v>2</v>
+      </c>
+      <c r="D171">
+        <v>1</v>
+      </c>
+      <c r="E171" t="s">
+        <v>85</v>
+      </c>
+      <c r="F171" t="s">
+        <v>14</v>
+      </c>
+      <c r="G171" t="s">
         <v>346</v>
-      </c>
-      <c r="C171">
-        <v>2</v>
-      </c>
-      <c r="D171">
-        <v>2</v>
-      </c>
-      <c r="E171" t="s">
-        <v>103</v>
-      </c>
-      <c r="F171" t="s">
-        <v>14</v>
-      </c>
-      <c r="G171" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.25">
@@ -7357,22 +7357,22 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
+        <v>347</v>
+      </c>
+      <c r="C172">
+        <v>2</v>
+      </c>
+      <c r="D172">
+        <v>2</v>
+      </c>
+      <c r="E172" t="s">
+        <v>32</v>
+      </c>
+      <c r="F172" t="s">
+        <v>21</v>
+      </c>
+      <c r="G172" t="s">
         <v>348</v>
-      </c>
-      <c r="C172">
-        <v>2</v>
-      </c>
-      <c r="D172">
-        <v>2</v>
-      </c>
-      <c r="E172" t="s">
-        <v>17</v>
-      </c>
-      <c r="F172" t="s">
-        <v>14</v>
-      </c>
-      <c r="G172" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.25">
@@ -7389,10 +7389,10 @@
         <v>2</v>
       </c>
       <c r="E173" t="s">
-        <v>30</v>
+        <v>213</v>
       </c>
       <c r="F173" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G173" t="s">
         <v>350</v>
@@ -7412,13 +7412,13 @@
         <v>2</v>
       </c>
       <c r="E174" t="s">
-        <v>190</v>
+        <v>17</v>
       </c>
       <c r="F174" t="s">
         <v>14</v>
       </c>
       <c r="G174" t="s">
-        <v>352</v>
+        <v>86</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.25">
@@ -7426,22 +7426,22 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
+        <v>352</v>
+      </c>
+      <c r="C175">
+        <v>2</v>
+      </c>
+      <c r="D175">
+        <v>2</v>
+      </c>
+      <c r="E175" t="s">
+        <v>30</v>
+      </c>
+      <c r="F175" t="s">
+        <v>14</v>
+      </c>
+      <c r="G175" t="s">
         <v>353</v>
-      </c>
-      <c r="C175">
-        <v>2</v>
-      </c>
-      <c r="D175">
-        <v>2</v>
-      </c>
-      <c r="E175" t="s">
-        <v>13</v>
-      </c>
-      <c r="F175" t="s">
-        <v>14</v>
-      </c>
-      <c r="G175" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.25">
@@ -7455,10 +7455,10 @@
         <v>2</v>
       </c>
       <c r="D176">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E176" t="s">
-        <v>41</v>
+        <v>192</v>
       </c>
       <c r="F176" t="s">
         <v>14</v>
@@ -7619,10 +7619,10 @@
         <v>2</v>
       </c>
       <c r="E183" t="s">
-        <v>116</v>
+        <v>51</v>
       </c>
       <c r="F183" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G183" t="s">
         <v>368</v>
@@ -7665,10 +7665,10 @@
         <v>2</v>
       </c>
       <c r="E185" t="s">
-        <v>51</v>
+        <v>116</v>
       </c>
       <c r="F185" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G185" t="s">
         <v>372</v>
@@ -7846,16 +7846,16 @@
         <v>2</v>
       </c>
       <c r="D193">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E193" t="s">
-        <v>20</v>
+        <v>77</v>
       </c>
       <c r="F193" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G193" t="s">
-        <v>386</v>
+        <v>86</v>
       </c>
     </row>
     <row r="194" spans="1:7" x14ac:dyDescent="0.25">
@@ -7863,22 +7863,22 @@
         <v>193</v>
       </c>
       <c r="B194" t="s">
+        <v>386</v>
+      </c>
+      <c r="C194">
+        <v>2</v>
+      </c>
+      <c r="D194">
+        <v>2</v>
+      </c>
+      <c r="E194" t="s">
+        <v>20</v>
+      </c>
+      <c r="F194" t="s">
+        <v>21</v>
+      </c>
+      <c r="G194" t="s">
         <v>387</v>
-      </c>
-      <c r="C194">
-        <v>2</v>
-      </c>
-      <c r="D194">
-        <v>1</v>
-      </c>
-      <c r="E194" t="s">
-        <v>77</v>
-      </c>
-      <c r="F194" t="s">
-        <v>14</v>
-      </c>
-      <c r="G194" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="195" spans="1:7" x14ac:dyDescent="0.25">
@@ -8332,7 +8332,7 @@
         <v>1</v>
       </c>
       <c r="E214" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F214" t="s">
         <v>14</v>
@@ -8769,7 +8769,7 @@
         <v>2</v>
       </c>
       <c r="E233" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F233" t="s">
         <v>14</v>
@@ -8815,7 +8815,7 @@
         <v>1</v>
       </c>
       <c r="E235" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F235" t="s">
         <v>14</v>
@@ -8861,7 +8861,7 @@
         <v>2</v>
       </c>
       <c r="E237" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="F237" t="s">
         <v>14</v>
@@ -8973,7 +8973,7 @@
         <v>2</v>
       </c>
       <c r="D242">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E242" t="s">
         <v>116</v>
@@ -8982,7 +8982,7 @@
         <v>21</v>
       </c>
       <c r="G242" t="s">
-        <v>402</v>
+        <v>476</v>
       </c>
     </row>
     <row r="243" spans="1:7" x14ac:dyDescent="0.25">
@@ -8990,7 +8990,7 @@
         <v>242</v>
       </c>
       <c r="B243" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C243">
         <v>2</v>
@@ -8999,10 +8999,10 @@
         <v>1</v>
       </c>
       <c r="E243" t="s">
-        <v>32</v>
+        <v>116</v>
       </c>
       <c r="F243" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G243" t="s">
         <v>402</v>
@@ -9013,22 +9013,22 @@
         <v>243</v>
       </c>
       <c r="B244" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="C244">
         <v>2</v>
       </c>
       <c r="D244">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E244" t="s">
-        <v>116</v>
+        <v>32</v>
       </c>
       <c r="F244" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G244" t="s">
-        <v>478</v>
+        <v>402</v>
       </c>
     </row>
     <row r="245" spans="1:7" x14ac:dyDescent="0.25">
@@ -9068,10 +9068,10 @@
         <v>1</v>
       </c>
       <c r="E246" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="F246" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G246" t="s">
         <v>482</v>
@@ -9091,10 +9091,10 @@
         <v>1</v>
       </c>
       <c r="E247" t="s">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="F247" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G247" t="s">
         <v>484</v>
@@ -9183,10 +9183,10 @@
         <v>2</v>
       </c>
       <c r="E251" t="s">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="F251" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G251" t="s">
         <v>492</v>
@@ -9203,10 +9203,10 @@
         <v>2</v>
       </c>
       <c r="D252">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E252" t="s">
-        <v>41</v>
+        <v>103</v>
       </c>
       <c r="F252" t="s">
         <v>14</v>
@@ -9229,7 +9229,7 @@
         <v>2</v>
       </c>
       <c r="E253" t="s">
-        <v>190</v>
+        <v>77</v>
       </c>
       <c r="F253" t="s">
         <v>14</v>
@@ -9252,10 +9252,10 @@
         <v>2</v>
       </c>
       <c r="E254" t="s">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="F254" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G254" t="s">
         <v>498</v>
@@ -9272,13 +9272,13 @@
         <v>2</v>
       </c>
       <c r="D255">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E255" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="F255" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G255" t="s">
         <v>500</v>
@@ -9321,7 +9321,7 @@
         <v>2</v>
       </c>
       <c r="E257" t="s">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="F257" t="s">
         <v>14</v>
@@ -9344,10 +9344,10 @@
         <v>2</v>
       </c>
       <c r="E258" t="s">
-        <v>77</v>
+        <v>27</v>
       </c>
       <c r="F258" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G258" t="s">
         <v>506</v>
@@ -9456,16 +9456,16 @@
         <v>2</v>
       </c>
       <c r="D263">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E263" t="s">
+        <v>41</v>
+      </c>
+      <c r="F263" t="s">
+        <v>14</v>
+      </c>
+      <c r="G263" t="s">
         <v>515</v>
-      </c>
-      <c r="F263" t="s">
-        <v>14</v>
-      </c>
-      <c r="G263" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="264" spans="1:7" x14ac:dyDescent="0.25">
@@ -9473,16 +9473,16 @@
         <v>263</v>
       </c>
       <c r="B264" t="s">
+        <v>516</v>
+      </c>
+      <c r="C264">
+        <v>2</v>
+      </c>
+      <c r="D264">
+        <v>2</v>
+      </c>
+      <c r="E264" t="s">
         <v>517</v>
-      </c>
-      <c r="C264">
-        <v>2</v>
-      </c>
-      <c r="D264">
-        <v>1</v>
-      </c>
-      <c r="E264" t="s">
-        <v>41</v>
       </c>
       <c r="F264" t="s">
         <v>14</v>
@@ -9551,10 +9551,10 @@
         <v>521</v>
       </c>
       <c r="C3">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="D3">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E3" t="s">
         <v>31</v>
@@ -10364,7 +10364,7 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>602</v>
+        <v>1</v>
       </c>
       <c r="C51">
         <v>7</v>
@@ -10373,7 +10373,7 @@
         <v>7</v>
       </c>
       <c r="E51" t="s">
-        <v>603</v>
+        <v>86</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
@@ -10381,7 +10381,7 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C52">
         <v>7</v>
@@ -10390,7 +10390,7 @@
         <v>7</v>
       </c>
       <c r="E52" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -10398,7 +10398,7 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>1</v>
+        <v>604</v>
       </c>
       <c r="C53">
         <v>7</v>
@@ -10407,7 +10407,7 @@
         <v>7</v>
       </c>
       <c r="E53" t="s">
-        <v>86</v>
+        <v>605</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -10560,7 +10560,7 @@
         <v>5</v>
       </c>
       <c r="E62" t="s">
-        <v>28</v>
+        <v>621</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -10568,7 +10568,7 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="C63">
         <v>5</v>
@@ -10577,7 +10577,7 @@
         <v>5</v>
       </c>
       <c r="E63" t="s">
-        <v>622</v>
+        <v>28</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
@@ -10778,7 +10778,7 @@
         <v>4</v>
       </c>
       <c r="D75">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E75" t="s">
         <v>645</v>
@@ -10795,7 +10795,7 @@
         <v>4</v>
       </c>
       <c r="D76">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E76" t="s">
         <v>647</v>
@@ -10829,7 +10829,7 @@
         <v>4</v>
       </c>
       <c r="D78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E78" t="s">
         <v>651</v>
@@ -10846,7 +10846,7 @@
         <v>4</v>
       </c>
       <c r="D79">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E79" t="s">
         <v>653</v>
@@ -10863,10 +10863,10 @@
         <v>4</v>
       </c>
       <c r="D80">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" t="s">
-        <v>86</v>
+        <v>655</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -10874,16 +10874,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C81">
         <v>4</v>
       </c>
       <c r="D81">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E81" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -10891,16 +10891,16 @@
         <v>81</v>
       </c>
       <c r="B82" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C82">
         <v>4</v>
       </c>
       <c r="D82">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>658</v>
+        <v>86</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -11019,7 +11019,7 @@
         <v>4</v>
       </c>
       <c r="E89" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
@@ -11985,7 +11985,7 @@
         <v>2</v>
       </c>
       <c r="D146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E146" t="s">
         <v>777</v>
@@ -12002,7 +12002,7 @@
         <v>2</v>
       </c>
       <c r="D147">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E147" t="s">
         <v>779</v>
@@ -12039,7 +12039,7 @@
         <v>2</v>
       </c>
       <c r="E149" t="s">
-        <v>86</v>
+        <v>783</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -12047,7 +12047,7 @@
         <v>149</v>
       </c>
       <c r="B150" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C150">
         <v>2</v>
@@ -12056,7 +12056,7 @@
         <v>2</v>
       </c>
       <c r="E150" t="s">
-        <v>784</v>
+        <v>86</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -12257,7 +12257,7 @@
         <v>2</v>
       </c>
       <c r="D162">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E162" t="s">
         <v>808</v>
@@ -12274,7 +12274,7 @@
         <v>2</v>
       </c>
       <c r="D163">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E163" t="s">
         <v>810</v>
@@ -12291,7 +12291,7 @@
         <v>2</v>
       </c>
       <c r="D164">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E164" t="s">
         <v>812</v>
@@ -12311,7 +12311,7 @@
         <v>1</v>
       </c>
       <c r="E165" t="s">
-        <v>86</v>
+        <v>814</v>
       </c>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.25">
@@ -12319,7 +12319,7 @@
         <v>165</v>
       </c>
       <c r="B166" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="C166">
         <v>2</v>
@@ -12328,7 +12328,7 @@
         <v>2</v>
       </c>
       <c r="E166" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
@@ -12336,7 +12336,7 @@
         <v>166</v>
       </c>
       <c r="B167" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="C167">
         <v>2</v>
@@ -12345,7 +12345,7 @@
         <v>2</v>
       </c>
       <c r="E167" t="s">
-        <v>622</v>
+        <v>818</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
@@ -12353,16 +12353,16 @@
         <v>167</v>
       </c>
       <c r="B168" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
       <c r="C168">
         <v>2</v>
       </c>
       <c r="D168">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E168" t="s">
-        <v>818</v>
+        <v>86</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
@@ -12370,16 +12370,16 @@
         <v>168</v>
       </c>
       <c r="B169" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="C169">
         <v>2</v>
       </c>
       <c r="D169">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E169" t="s">
-        <v>86</v>
+        <v>821</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -12387,16 +12387,16 @@
         <v>169</v>
       </c>
       <c r="B170" t="s">
-        <v>820</v>
+        <v>822</v>
       </c>
       <c r="C170">
         <v>2</v>
       </c>
       <c r="D170">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E170" t="s">
-        <v>86</v>
+        <v>624</v>
       </c>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.25">
@@ -12404,7 +12404,7 @@
         <v>170</v>
       </c>
       <c r="B171" t="s">
-        <v>821</v>
+        <v>823</v>
       </c>
       <c r="C171">
         <v>2</v>
@@ -12413,7 +12413,7 @@
         <v>2</v>
       </c>
       <c r="E171" t="s">
-        <v>822</v>
+        <v>824</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
@@ -12421,7 +12421,7 @@
         <v>171</v>
       </c>
       <c r="B172" t="s">
-        <v>823</v>
+        <v>825</v>
       </c>
       <c r="C172">
         <v>2</v>
@@ -12438,16 +12438,16 @@
         <v>172</v>
       </c>
       <c r="B173" t="s">
-        <v>824</v>
+        <v>826</v>
       </c>
       <c r="C173">
         <v>2</v>
       </c>
       <c r="D173">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E173" t="s">
-        <v>825</v>
+        <v>86</v>
       </c>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.25">
@@ -12455,16 +12455,16 @@
         <v>173</v>
       </c>
       <c r="B174" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C174">
         <v>2</v>
       </c>
       <c r="D174">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E174" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.25">
@@ -12472,7 +12472,7 @@
         <v>174</v>
       </c>
       <c r="B175" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C175">
         <v>2</v>
@@ -12481,7 +12481,7 @@
         <v>1</v>
       </c>
       <c r="E175" t="s">
-        <v>829</v>
+        <v>86</v>
       </c>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.25">
@@ -13399,7 +13399,7 @@
         <v>2</v>
       </c>
       <c r="E229" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.25">
@@ -13685,7 +13685,7 @@
         <v>2</v>
       </c>
       <c r="D246">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E246" t="s">
         <v>956</v>
@@ -13719,7 +13719,7 @@
         <v>2</v>
       </c>
       <c r="D248">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E248" t="s">
         <v>960</v>
@@ -13756,7 +13756,7 @@
         <v>2</v>
       </c>
       <c r="E250" t="s">
-        <v>964</v>
+        <v>490</v>
       </c>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.25">
@@ -13764,16 +13764,16 @@
         <v>250</v>
       </c>
       <c r="B251" t="s">
+        <v>964</v>
+      </c>
+      <c r="C251">
+        <v>2</v>
+      </c>
+      <c r="D251">
+        <v>2</v>
+      </c>
+      <c r="E251" t="s">
         <v>965</v>
-      </c>
-      <c r="C251">
-        <v>2</v>
-      </c>
-      <c r="D251">
-        <v>2</v>
-      </c>
-      <c r="E251" t="s">
-        <v>966</v>
       </c>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.25">
@@ -13781,16 +13781,16 @@
         <v>251</v>
       </c>
       <c r="B252" t="s">
+        <v>966</v>
+      </c>
+      <c r="C252">
+        <v>2</v>
+      </c>
+      <c r="D252">
+        <v>2</v>
+      </c>
+      <c r="E252" t="s">
         <v>967</v>
-      </c>
-      <c r="C252">
-        <v>2</v>
-      </c>
-      <c r="D252">
-        <v>2</v>
-      </c>
-      <c r="E252" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.25">
@@ -14049,7 +14049,7 @@
         <v>996</v>
       </c>
       <c r="B5">
-        <v>15147</v>
+        <v>15145</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -14057,7 +14057,7 @@
         <v>997</v>
       </c>
       <c r="B6">
-        <v>2763</v>
+        <v>2773</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -14065,7 +14065,7 @@
         <v>998</v>
       </c>
       <c r="B7">
-        <v>4085</v>
+        <v>4075</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -14073,7 +14073,7 @@
         <v>999</v>
       </c>
       <c r="B8">
-        <v>8299</v>
+        <v>8297</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
